--- a/output/tables/Table1a_Percent_Support.xlsx
+++ b/output/tables/Table1a_Percent_Support.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="276" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="276" uniqueCount="258">
   <si>
     <t>Table 1a. Percent somewhat or strongly supporting SNAP soft-drink/candy restrictions, by subgroup and SNAP participation (N = 8715)</t>
   </si>
@@ -21,25 +21,25 @@
     <t>Variable</t>
   </si>
   <si>
-    <t>Overall</t>
-  </si>
-  <si>
-    <t>Non-SNAP</t>
-  </si>
-  <si>
-    <t>SNAP</t>
+    <t>Overall, % (SE)</t>
+  </si>
+  <si>
+    <t>Non-SNAP, % (SE)</t>
+  </si>
+  <si>
+    <t>SNAP, % (SE)</t>
   </si>
   <si>
     <t>Total sample</t>
   </si>
   <si>
-    <t>3892 (44.7)</t>
-  </si>
-  <si>
-    <t>2422 (55.8)</t>
-  </si>
-  <si>
-    <t>1470 (33.6)</t>
+    <t>44.7 (0.5)</t>
+  </si>
+  <si>
+    <t>55.8 (0.8)</t>
+  </si>
+  <si>
+    <t>33.6 (0.7)</t>
   </si>
   <si>
     <t>Psychological predictors</t>
@@ -51,244 +51,241 @@
     <t xml:space="preserve">   1</t>
   </si>
   <si>
-    <t>1868 (49.3)</t>
-  </si>
-  <si>
-    <t>1259 (60.6)</t>
-  </si>
-  <si>
-    <t>609 (35.6)</t>
+    <t>49.3 (0.8)</t>
+  </si>
+  <si>
+    <t>60.6 (1.1)</t>
+  </si>
+  <si>
+    <t>35.6 (1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   2</t>
   </si>
   <si>
-    <t>1001 (39.5)</t>
-  </si>
-  <si>
-    <t>607 (51.3)</t>
-  </si>
-  <si>
-    <t>394 (29.2)</t>
+    <t>39.5 (1.0)</t>
+  </si>
+  <si>
+    <t>51.3 (1.5)</t>
+  </si>
+  <si>
+    <t>29.2 (1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   3</t>
   </si>
   <si>
-    <t>476 (41.1)</t>
-  </si>
-  <si>
-    <t>247 (48.7)</t>
-  </si>
-  <si>
-    <t>229 (35.1)</t>
+    <t>41.1 (1.4)</t>
+  </si>
+  <si>
+    <t>48.7 (2.2)</t>
+  </si>
+  <si>
+    <t>35.1 (1.9)</t>
   </si>
   <si>
     <t xml:space="preserve">   4</t>
   </si>
   <si>
-    <t>547 (44.4)</t>
-  </si>
-  <si>
-    <t>309 (54.0)</t>
-  </si>
-  <si>
-    <t>238 (36.1)</t>
+    <t>44.4 (1.4)</t>
+  </si>
+  <si>
+    <t>54.0 (2.1)</t>
+  </si>
+  <si>
+    <t>36.1 (1.9)</t>
   </si>
   <si>
     <t>Perceived health risk of soda</t>
   </si>
   <si>
-    <t>203 (30.6)</t>
-  </si>
-  <si>
-    <t>111 (42.7)</t>
-  </si>
-  <si>
-    <t>92 (22.8)</t>
-  </si>
-  <si>
-    <t>766 (36.7)</t>
-  </si>
-  <si>
-    <t>452 (47.2)</t>
-  </si>
-  <si>
-    <t>314 (27.8)</t>
-  </si>
-  <si>
-    <t>1314 (42.8)</t>
-  </si>
-  <si>
-    <t>871 (53.9)</t>
-  </si>
-  <si>
-    <t>443 (30.5)</t>
-  </si>
-  <si>
-    <t>1015 (54.2)</t>
-  </si>
-  <si>
-    <t>672 (65.6)</t>
-  </si>
-  <si>
-    <t>343 (40.5)</t>
+    <t>30.6 (1.8)</t>
+  </si>
+  <si>
+    <t>42.7 (3.1)</t>
+  </si>
+  <si>
+    <t>22.8 (2.1)</t>
+  </si>
+  <si>
+    <t>36.7 (1.1)</t>
+  </si>
+  <si>
+    <t>47.2 (1.6)</t>
+  </si>
+  <si>
+    <t>27.8 (1.3)</t>
+  </si>
+  <si>
+    <t>42.8 (0.9)</t>
+  </si>
+  <si>
+    <t>53.9 (1.2)</t>
+  </si>
+  <si>
+    <t>30.5 (1.2)</t>
+  </si>
+  <si>
+    <t>54.2 (1.2)</t>
+  </si>
+  <si>
+    <t>65.6 (1.5)</t>
+  </si>
+  <si>
+    <t>40.5 (1.7)</t>
   </si>
   <si>
     <t xml:space="preserve">   5</t>
   </si>
   <si>
-    <t>594 (58.0)</t>
-  </si>
-  <si>
-    <t>316 (65.7)</t>
-  </si>
-  <si>
-    <t>278 (51.1)</t>
+    <t>58.0 (1.5)</t>
+  </si>
+  <si>
+    <t>65.7 (2.2)</t>
+  </si>
+  <si>
+    <t>51.1 (2.1)</t>
   </si>
   <si>
     <t>Embarrassment when paying with SNAP</t>
   </si>
   <si>
-    <t>873 (37.9)</t>
-  </si>
-  <si>
-    <t>286 (58.2)</t>
-  </si>
-  <si>
-    <t>587 (32.4)</t>
-  </si>
-  <si>
-    <t>801 (48.6)</t>
-  </si>
-  <si>
-    <t>466 (65.2)</t>
-  </si>
-  <si>
-    <t>335 (35.9)</t>
-  </si>
-  <si>
-    <t>1453 (49.9)</t>
-  </si>
-  <si>
-    <t>1099 (59.3)</t>
-  </si>
-  <si>
-    <t>354 (33.4)</t>
-  </si>
-  <si>
-    <t>556 (44.4)</t>
-  </si>
-  <si>
-    <t>458 (48.1)</t>
-  </si>
-  <si>
-    <t>98 (32.7)</t>
-  </si>
-  <si>
-    <t>209 (34.8)</t>
-  </si>
-  <si>
-    <t>113 (34.5)</t>
-  </si>
-  <si>
-    <t>96 (35.3)</t>
+    <t>37.9 (1.0)</t>
+  </si>
+  <si>
+    <t>58.2 (2.2)</t>
+  </si>
+  <si>
+    <t>32.4 (1.1)</t>
+  </si>
+  <si>
+    <t>48.6 (1.2)</t>
+  </si>
+  <si>
+    <t>65.2 (1.8)</t>
+  </si>
+  <si>
+    <t>35.9 (1.6)</t>
+  </si>
+  <si>
+    <t>49.9 (0.9)</t>
+  </si>
+  <si>
+    <t>59.3 (1.1)</t>
+  </si>
+  <si>
+    <t>33.4 (1.4)</t>
+  </si>
+  <si>
+    <t>48.1 (1.6)</t>
+  </si>
+  <si>
+    <t>32.7 (2.7)</t>
+  </si>
+  <si>
+    <t>34.8 (1.9)</t>
+  </si>
+  <si>
+    <t>34.5 (2.6)</t>
+  </si>
+  <si>
+    <t>35.3 (2.9)</t>
   </si>
   <si>
     <t>Perceived stigma of SNAP policies</t>
   </si>
   <si>
-    <t>991 (65.3)</t>
-  </si>
-  <si>
-    <t>672 (84.8)</t>
-  </si>
-  <si>
-    <t>319 (44.0)</t>
+    <t>65.3 (1.2)</t>
+  </si>
+  <si>
+    <t>84.8 (1.3)</t>
+  </si>
+  <si>
+    <t>44.0 (1.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   1.5</t>
   </si>
   <si>
-    <t>180 (51.6)</t>
-  </si>
-  <si>
-    <t>118 (70.7)</t>
-  </si>
-  <si>
-    <t>62 (34.1)</t>
-  </si>
-  <si>
-    <t>550 (54.7)</t>
-  </si>
-  <si>
-    <t>373 (67.9)</t>
-  </si>
-  <si>
-    <t>177 (38.8)</t>
+    <t>51.6 (2.7)</t>
+  </si>
+  <si>
+    <t>70.7 (3.5)</t>
+  </si>
+  <si>
+    <t>34.1 (3.5)</t>
+  </si>
+  <si>
+    <t>54.7 (1.6)</t>
+  </si>
+  <si>
+    <t>67.9 (2.0)</t>
+  </si>
+  <si>
+    <t>38.8 (2.3)</t>
   </si>
   <si>
     <t xml:space="preserve">   2.5</t>
   </si>
   <si>
-    <t>313 (46.4)</t>
-  </si>
-  <si>
-    <t>198 (56.6)</t>
-  </si>
-  <si>
-    <t>115 (35.5)</t>
-  </si>
-  <si>
-    <t>1051 (39.0)</t>
-  </si>
-  <si>
-    <t>738 (49.3)</t>
-  </si>
-  <si>
-    <t>313 (26.1)</t>
+    <t>46.4 (1.9)</t>
+  </si>
+  <si>
+    <t>56.6 (2.6)</t>
+  </si>
+  <si>
+    <t>35.5 (2.7)</t>
+  </si>
+  <si>
+    <t>39.0 (0.9)</t>
+  </si>
+  <si>
+    <t>49.3 (1.3)</t>
+  </si>
+  <si>
+    <t>26.1 (1.3)</t>
   </si>
   <si>
     <t xml:space="preserve">   3.5</t>
   </si>
   <si>
-    <t>248 (36.0)</t>
-  </si>
-  <si>
-    <t>127 (42.8)</t>
-  </si>
-  <si>
-    <t>121 (30.9)</t>
-  </si>
-  <si>
-    <t>280 (32.4)</t>
-  </si>
-  <si>
-    <t>124 (32.7)</t>
-  </si>
-  <si>
-    <t>156 (32.2)</t>
+    <t>36.0 (1.8)</t>
+  </si>
+  <si>
+    <t>42.8 (2.9)</t>
+  </si>
+  <si>
+    <t>30.9 (2.3)</t>
+  </si>
+  <si>
+    <t>32.4 (1.6)</t>
+  </si>
+  <si>
+    <t>32.7 (2.4)</t>
+  </si>
+  <si>
+    <t>32.2 (2.1)</t>
   </si>
   <si>
     <t xml:space="preserve">   4.5</t>
   </si>
   <si>
-    <t>82 (30.3)</t>
-  </si>
-  <si>
-    <t>27 (29.3)</t>
-  </si>
-  <si>
-    <t>55 (30.7)</t>
-  </si>
-  <si>
-    <t>197 (30.3)</t>
-  </si>
-  <si>
-    <t>45 (20.7)</t>
-  </si>
-  <si>
-    <t>152 (35.1)</t>
+    <t>30.3 (2.8)</t>
+  </si>
+  <si>
+    <t>29.3 (4.7)</t>
+  </si>
+  <si>
+    <t>30.7 (3.4)</t>
+  </si>
+  <si>
+    <t>30.3 (1.8)</t>
+  </si>
+  <si>
+    <t>20.7 (2.8)</t>
+  </si>
+  <si>
+    <t>35.1 (2.3)</t>
   </si>
   <si>
     <t>Covariates</t>
@@ -300,85 +297,85 @@
     <t xml:space="preserve">   18-20</t>
   </si>
   <si>
-    <t>4 (50.0)</t>
-  </si>
-  <si>
-    <t>1 (33.3)</t>
-  </si>
-  <si>
-    <t>3 (60.0)</t>
+    <t>50.0 (17.7)</t>
+  </si>
+  <si>
+    <t>33.3 (27.2)</t>
+  </si>
+  <si>
+    <t>60.0 (21.9)</t>
   </si>
   <si>
     <t xml:space="preserve">   21-24</t>
   </si>
   <si>
-    <t>27 (42.9)</t>
-  </si>
-  <si>
-    <t>7 (31.8)</t>
-  </si>
-  <si>
-    <t>20 (48.8)</t>
+    <t>42.9 (6.2)</t>
+  </si>
+  <si>
+    <t>31.8 (9.9)</t>
+  </si>
+  <si>
+    <t>48.8 (7.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   25-34</t>
   </si>
   <si>
-    <t>319 (38.8)</t>
-  </si>
-  <si>
-    <t>164 (45.7)</t>
-  </si>
-  <si>
-    <t>155 (33.4)</t>
+    <t>38.8 (1.7)</t>
+  </si>
+  <si>
+    <t>45.7 (2.6)</t>
+  </si>
+  <si>
+    <t>33.4 (2.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   35-44</t>
   </si>
   <si>
-    <t>637 (40.1)</t>
-  </si>
-  <si>
-    <t>371 (49.4)</t>
-  </si>
-  <si>
-    <t>266 (31.8)</t>
+    <t>40.1 (1.2)</t>
+  </si>
+  <si>
+    <t>49.4 (1.8)</t>
+  </si>
+  <si>
+    <t>31.8 (1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">   45-54</t>
   </si>
   <si>
-    <t>774 (43.6)</t>
-  </si>
-  <si>
-    <t>486 (54.5)</t>
-  </si>
-  <si>
-    <t>288 (32.6)</t>
+    <t>43.6 (1.2)</t>
+  </si>
+  <si>
+    <t>54.5 (1.7)</t>
+  </si>
+  <si>
+    <t>32.6 (1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">   55-64</t>
   </si>
   <si>
-    <t>979 (44.0)</t>
-  </si>
-  <si>
-    <t>619 (57.0)</t>
-  </si>
-  <si>
-    <t>360 (31.7)</t>
+    <t>44.0 (1.1)</t>
+  </si>
+  <si>
+    <t>57.0 (1.5)</t>
+  </si>
+  <si>
+    <t>31.7 (1.4)</t>
   </si>
   <si>
     <t xml:space="preserve">   65+</t>
   </si>
   <si>
-    <t>1152 (51.5)</t>
-  </si>
-  <si>
-    <t>774 (63.1)</t>
-  </si>
-  <si>
-    <t>378 (37.5)</t>
+    <t>51.5 (1.1)</t>
+  </si>
+  <si>
+    <t>63.1 (1.4)</t>
+  </si>
+  <si>
+    <t>37.5 (1.5)</t>
   </si>
   <si>
     <t>gender</t>
@@ -387,37 +384,37 @@
     <t xml:space="preserve">   Female</t>
   </si>
   <si>
-    <t>2936 (44.2)</t>
-  </si>
-  <si>
-    <t>1866 (55.8)</t>
-  </si>
-  <si>
-    <t>1070 (32.4)</t>
+    <t>44.2 (0.6)</t>
+  </si>
+  <si>
+    <t>55.8 (0.9)</t>
+  </si>
+  <si>
+    <t>32.4 (0.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   Male</t>
   </si>
   <si>
-    <t>923 (46.6)</t>
-  </si>
-  <si>
-    <t>543 (56.2)</t>
-  </si>
-  <si>
-    <t>380 (37.4)</t>
+    <t>46.6 (1.1)</t>
+  </si>
+  <si>
+    <t>56.2 (1.6)</t>
+  </si>
+  <si>
+    <t>37.4 (1.5)</t>
   </si>
   <si>
     <t xml:space="preserve">   Other</t>
   </si>
   <si>
-    <t>33 (35.5)</t>
-  </si>
-  <si>
-    <t>13 (40.6)</t>
-  </si>
-  <si>
-    <t>20 (32.8)</t>
+    <t>35.5 (5.0)</t>
+  </si>
+  <si>
+    <t>40.6 (8.7)</t>
+  </si>
+  <si>
+    <t>32.8 (6.0)</t>
   </si>
   <si>
     <t>ethnicity</t>
@@ -426,58 +423,58 @@
     <t xml:space="preserve">   White/Caucasian</t>
   </si>
   <si>
-    <t>2743 (49.6)</t>
-  </si>
-  <si>
-    <t>1908 (61.4)</t>
-  </si>
-  <si>
-    <t>835 (34.5)</t>
+    <t>49.6 (0.7)</t>
+  </si>
+  <si>
+    <t>61.4 (0.9)</t>
+  </si>
+  <si>
+    <t>34.5 (1.0)</t>
   </si>
   <si>
     <t xml:space="preserve">   Asian</t>
   </si>
   <si>
-    <t>182 (46.7)</t>
-  </si>
-  <si>
-    <t>103 (52.8)</t>
-  </si>
-  <si>
-    <t>79 (40.5)</t>
+    <t>46.7 (2.5)</t>
+  </si>
+  <si>
+    <t>52.8 (3.6)</t>
+  </si>
+  <si>
+    <t>40.5 (3.5)</t>
   </si>
   <si>
     <t xml:space="preserve">   Black or African American</t>
   </si>
   <si>
-    <t>381 (26.9)</t>
-  </si>
-  <si>
-    <t>156 (29.4)</t>
-  </si>
-  <si>
-    <t>225 (25.4)</t>
+    <t>26.9 (1.2)</t>
+  </si>
+  <si>
+    <t>29.4 (2.0)</t>
+  </si>
+  <si>
+    <t>25.4 (1.5)</t>
   </si>
   <si>
     <t xml:space="preserve">   Hispanic/Latino</t>
   </si>
   <si>
-    <t>520 (43.4)</t>
-  </si>
-  <si>
-    <t>221 (51.6)</t>
-  </si>
-  <si>
-    <t>299 (38.9)</t>
-  </si>
-  <si>
-    <t>66 (36.3)</t>
-  </si>
-  <si>
-    <t>34 (42.5)</t>
-  </si>
-  <si>
-    <t>32 (31.4)</t>
+    <t>43.4 (1.4)</t>
+  </si>
+  <si>
+    <t>51.6 (2.4)</t>
+  </si>
+  <si>
+    <t>38.9 (1.8)</t>
+  </si>
+  <si>
+    <t>36.3 (3.6)</t>
+  </si>
+  <si>
+    <t>42.5 (5.5)</t>
+  </si>
+  <si>
+    <t>31.4 (4.6)</t>
   </si>
   <si>
     <t>education</t>
@@ -486,97 +483,97 @@
     <t xml:space="preserve">   Less than high school</t>
   </si>
   <si>
-    <t>126 (36.8)</t>
-  </si>
-  <si>
-    <t>36 (40.4)</t>
-  </si>
-  <si>
-    <t>90 (35.6)</t>
+    <t>36.8 (2.6)</t>
+  </si>
+  <si>
+    <t>40.4 (5.2)</t>
+  </si>
+  <si>
+    <t>35.6 (3.0)</t>
   </si>
   <si>
     <t xml:space="preserve">   High School/GED</t>
   </si>
   <si>
-    <t>857 (40.3)</t>
-  </si>
-  <si>
-    <t>462 (53.4)</t>
-  </si>
-  <si>
-    <t>395 (31.3)</t>
+    <t>40.3 (1.1)</t>
+  </si>
+  <si>
+    <t>53.4 (1.7)</t>
+  </si>
+  <si>
+    <t>31.3 (1.3)</t>
   </si>
   <si>
     <t xml:space="preserve">   Trade/Technical Degree</t>
   </si>
   <si>
-    <t>247 (44.0)</t>
-  </si>
-  <si>
-    <t>135 (57.0)</t>
-  </si>
-  <si>
-    <t>112 (34.6)</t>
+    <t>44.0 (2.1)</t>
+  </si>
+  <si>
+    <t>57.0 (3.2)</t>
+  </si>
+  <si>
+    <t>34.6 (2.6)</t>
   </si>
   <si>
     <t xml:space="preserve">   Some College or university</t>
   </si>
   <si>
-    <t>842 (43.2)</t>
-  </si>
-  <si>
-    <t>507 (55.8)</t>
-  </si>
-  <si>
-    <t>335 (32.2)</t>
+    <t>43.2 (1.1)</t>
+  </si>
+  <si>
+    <t>55.8 (1.6)</t>
+  </si>
+  <si>
+    <t>32.2 (1.5)</t>
   </si>
   <si>
     <t xml:space="preserve">   2 year College Degree</t>
   </si>
   <si>
-    <t>459 (44.9)</t>
-  </si>
-  <si>
-    <t>268 (54.6)</t>
-  </si>
-  <si>
-    <t>191 (36.0)</t>
+    <t>44.9 (1.6)</t>
+  </si>
+  <si>
+    <t>54.6 (2.2)</t>
+  </si>
+  <si>
+    <t>36.0 (2.1)</t>
   </si>
   <si>
     <t xml:space="preserve">   4 year College Degree</t>
   </si>
   <si>
-    <t>794 (49.7)</t>
-  </si>
-  <si>
-    <t>578 (58.3)</t>
-  </si>
-  <si>
-    <t>216 (35.8)</t>
+    <t>49.7 (1.3)</t>
+  </si>
+  <si>
+    <t>58.3 (1.6)</t>
+  </si>
+  <si>
+    <t>35.8 (2.0)</t>
   </si>
   <si>
     <t xml:space="preserve">   Some Graduate School</t>
   </si>
   <si>
-    <t>119 (50.6)</t>
-  </si>
-  <si>
-    <t>75 (58.1)</t>
-  </si>
-  <si>
-    <t>44 (41.5)</t>
+    <t>50.6 (3.3)</t>
+  </si>
+  <si>
+    <t>58.1 (4.3)</t>
+  </si>
+  <si>
+    <t>41.5 (4.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   Graduate Degree</t>
   </si>
   <si>
-    <t>448 (50.6)</t>
-  </si>
-  <si>
-    <t>361 (57.5)</t>
-  </si>
-  <si>
-    <t>87 (33.9)</t>
+    <t>50.6 (1.7)</t>
+  </si>
+  <si>
+    <t>57.5 (2.0)</t>
+  </si>
+  <si>
+    <t>33.9 (3.0)</t>
   </si>
   <si>
     <t>income</t>
@@ -585,85 +582,82 @@
     <t xml:space="preserve">   - $20k</t>
   </si>
   <si>
-    <t>622 (32.6)</t>
-  </si>
-  <si>
-    <t>185 (44.3)</t>
-  </si>
-  <si>
-    <t>437 (29.3)</t>
+    <t>32.6 (1.1)</t>
+  </si>
+  <si>
+    <t>44.3 (2.4)</t>
+  </si>
+  <si>
+    <t>29.3 (1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   $20k-40k</t>
   </si>
   <si>
-    <t>713 (39.5)</t>
-  </si>
-  <si>
-    <t>338 (51.2)</t>
-  </si>
-  <si>
-    <t>375 (32.8)</t>
+    <t>39.5 (1.2)</t>
+  </si>
+  <si>
+    <t>51.2 (1.9)</t>
+  </si>
+  <si>
+    <t>32.8 (1.4)</t>
   </si>
   <si>
     <t xml:space="preserve">   $40k-60k</t>
   </si>
   <si>
-    <t>646 (44.3)</t>
-  </si>
-  <si>
-    <t>399 (52.4)</t>
-  </si>
-  <si>
-    <t>247 (35.5)</t>
+    <t>44.3 (1.3)</t>
+  </si>
+  <si>
+    <t>52.4 (1.8)</t>
+  </si>
+  <si>
+    <t>35.5 (1.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   $60k-80k</t>
   </si>
   <si>
-    <t>548 (51.4)</t>
-  </si>
-  <si>
-    <t>376 (57.9)</t>
-  </si>
-  <si>
-    <t>172 (41.1)</t>
+    <t>51.4 (1.5)</t>
+  </si>
+  <si>
+    <t>57.9 (1.9)</t>
+  </si>
+  <si>
+    <t>41.1 (2.4)</t>
   </si>
   <si>
     <t xml:space="preserve">   $80k-100k</t>
   </si>
   <si>
-    <t>408 (51.8)</t>
-  </si>
-  <si>
-    <t>309 (58.2)</t>
-  </si>
-  <si>
-    <t>99 (38.5)</t>
+    <t>51.8 (1.8)</t>
+  </si>
+  <si>
+    <t>58.2 (2.1)</t>
+  </si>
+  <si>
+    <t>38.5 (3.0)</t>
   </si>
   <si>
     <t xml:space="preserve">   $100k-125k</t>
   </si>
   <si>
-    <t>307 (53.6)</t>
-  </si>
-  <si>
-    <t>258 (58.6)</t>
-  </si>
-  <si>
-    <t>49 (36.8)</t>
+    <t>53.6 (2.1)</t>
+  </si>
+  <si>
+    <t>58.6 (2.3)</t>
+  </si>
+  <si>
+    <t>36.8 (4.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   $125k +</t>
   </si>
   <si>
-    <t>648 (58.0)</t>
-  </si>
-  <si>
-    <t>557 (63.3)</t>
-  </si>
-  <si>
-    <t>91 (38.4)</t>
+    <t>63.3 (1.6)</t>
+  </si>
+  <si>
+    <t>38.4 (3.2)</t>
   </si>
   <si>
     <t>user_census_region_name</t>
@@ -672,49 +666,46 @@
     <t xml:space="preserve">   Midwest</t>
   </si>
   <si>
-    <t>822 (45.0)</t>
-  </si>
-  <si>
-    <t>561 (58.7)</t>
-  </si>
-  <si>
-    <t>261 (29.9)</t>
+    <t>45.0 (1.2)</t>
+  </si>
+  <si>
+    <t>58.7 (1.6)</t>
+  </si>
+  <si>
+    <t>29.9 (1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">   Northeast</t>
   </si>
   <si>
-    <t>644 (43.9)</t>
-  </si>
-  <si>
-    <t>352 (55.5)</t>
-  </si>
-  <si>
-    <t>292 (35.1)</t>
+    <t>43.9 (1.3)</t>
+  </si>
+  <si>
+    <t>55.5 (2.0)</t>
+  </si>
+  <si>
+    <t>35.1 (1.7)</t>
   </si>
   <si>
     <t xml:space="preserve">   South</t>
   </si>
   <si>
-    <t>1758 (46.8)</t>
-  </si>
-  <si>
-    <t>1164 (55.9)</t>
-  </si>
-  <si>
-    <t>594 (35.5)</t>
+    <t>46.8 (0.8)</t>
+  </si>
+  <si>
+    <t>55.9 (1.1)</t>
+  </si>
+  <si>
+    <t>35.5 (1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   West</t>
   </si>
   <si>
-    <t>668 (40.1)</t>
-  </si>
-  <si>
-    <t>345 (51.7)</t>
-  </si>
-  <si>
-    <t>323 (32.4)</t>
+    <t>51.7 (1.9)</t>
+  </si>
+  <si>
+    <t>32.4 (1.5)</t>
   </si>
   <si>
     <t>has_children</t>
@@ -723,25 +714,25 @@
     <t xml:space="preserve">   No</t>
   </si>
   <si>
-    <t>2812 (46.4)</t>
-  </si>
-  <si>
-    <t>1844 (57.2)</t>
-  </si>
-  <si>
-    <t>968 (34.2)</t>
+    <t>46.4 (0.6)</t>
+  </si>
+  <si>
+    <t>57.2 (0.9)</t>
+  </si>
+  <si>
+    <t>34.2 (0.9)</t>
   </si>
   <si>
     <t xml:space="preserve">   Yes</t>
   </si>
   <si>
-    <t>1080 (40.6)</t>
-  </si>
-  <si>
-    <t>578 (51.7)</t>
-  </si>
-  <si>
-    <t>502 (32.5)</t>
+    <t>40.6 (1.0)</t>
+  </si>
+  <si>
+    <t>51.7 (1.5)</t>
+  </si>
+  <si>
+    <t>32.5 (1.2)</t>
   </si>
   <si>
     <t>State SNAP restriction status</t>
@@ -750,52 +741,52 @@
     <t xml:space="preserve">   Not adopted</t>
   </si>
   <si>
-    <t>1847 (41.5)</t>
-  </si>
-  <si>
-    <t>1019 (53.3)</t>
-  </si>
-  <si>
-    <t>828 (32.6)</t>
+    <t>41.5 (0.7)</t>
+  </si>
+  <si>
+    <t>53.3 (1.1)</t>
+  </si>
+  <si>
+    <t>32.6 (0.9)</t>
   </si>
   <si>
     <t xml:space="preserve">   Adopted not yet implemented or vacated</t>
   </si>
   <si>
-    <t>510 (41.2)</t>
-  </si>
-  <si>
-    <t>330 (54.4)</t>
-  </si>
-  <si>
-    <t>180 (28.5)</t>
+    <t>41.2 (1.4)</t>
+  </si>
+  <si>
+    <t>54.4 (2.0)</t>
+  </si>
+  <si>
+    <t>28.5 (1.8)</t>
   </si>
   <si>
     <t xml:space="preserve">   Previously implemented but vacated</t>
   </si>
   <si>
-    <t>169 (52.3)</t>
-  </si>
-  <si>
-    <t>145 (65.3)</t>
-  </si>
-  <si>
-    <t>24 (23.8)</t>
+    <t>52.3 (2.8)</t>
+  </si>
+  <si>
+    <t>65.3 (3.2)</t>
+  </si>
+  <si>
+    <t>23.8 (4.2)</t>
   </si>
   <si>
     <t xml:space="preserve">   Currently implemented</t>
   </si>
   <si>
-    <t>1366 (50.6)</t>
-  </si>
-  <si>
-    <t>928 (58.0)</t>
-  </si>
-  <si>
-    <t>438 (39.8)</t>
-  </si>
-  <si>
-    <t>Note. Complete-case analysis sample. Each cell is n (%): number and percent of respondents in that row subgroup (and SNAP column) who somewhat or strongly support removing soft drinks and candy from SNAP-eligible purchases. Denominators are the subgroup totals (not the full sample). Unweighted.</t>
+    <t>50.6 (1.0)</t>
+  </si>
+  <si>
+    <t>58.0 (1.2)</t>
+  </si>
+  <si>
+    <t>39.8 (1.5)</t>
+  </si>
+  <si>
+    <t>Note. Complete-case analysis sample. Each cell is the percent of respondents in that row subgroup (and SNAP column) who somewhat or strongly support removing soft drinks and candy from SNAP-eligible purchases, with the standard error of that percentage in parentheses: SE = 100 × sqrt[p(1−p)/n]. Unweighted.</t>
   </si>
 </sst>
 </file>
@@ -1068,13 +1059,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -1082,18 +1073,18 @@
         <v>40</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -1101,27 +1092,27 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
         <v>61</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>62</v>
-      </c>
-      <c r="D24" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -1129,27 +1120,27 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>69</v>
-      </c>
-      <c r="D26" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
         <v>71</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>72</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="28">
@@ -1157,27 +1148,27 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
         <v>75</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
         <v>78</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>79</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="30">
@@ -1185,27 +1176,27 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
         <v>82</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" t="s">
         <v>85</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="32">
@@ -1213,623 +1204,623 @@
         <v>40</v>
       </c>
       <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
         <v>89</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
         <v>94</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>95</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>96</v>
-      </c>
-      <c r="D36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
         <v>98</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>99</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
         <v>102</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>103</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
         <v>106</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>107</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>108</v>
-      </c>
-      <c r="D39" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
         <v>110</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>111</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>112</v>
-      </c>
-      <c r="D40" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
         <v>114</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>115</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" t="s">
         <v>118</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>119</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>120</v>
-      </c>
-      <c r="D42" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" t="s">
         <v>123</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>124</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>125</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" t="s">
         <v>127</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>128</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>129</v>
-      </c>
-      <c r="D45" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" t="s">
         <v>131</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>132</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>133</v>
-      </c>
-      <c r="D46" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" t="s">
         <v>136</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>137</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>138</v>
-      </c>
-      <c r="D48" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" t="s">
         <v>140</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>141</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>142</v>
-      </c>
-      <c r="D49" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" t="s">
         <v>144</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>145</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>146</v>
-      </c>
-      <c r="D50" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" t="s">
         <v>148</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>149</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>150</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" t="s">
         <v>152</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>153</v>
-      </c>
-      <c r="D52" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" t="s">
         <v>156</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>157</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>158</v>
-      </c>
-      <c r="D54" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" t="s">
         <v>160</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>161</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>162</v>
-      </c>
-      <c r="D55" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" t="s">
         <v>164</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>165</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>166</v>
-      </c>
-      <c r="D56" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
         <v>168</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>169</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>170</v>
-      </c>
-      <c r="D57" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" t="s">
         <v>172</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>173</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>174</v>
-      </c>
-      <c r="D58" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" t="s">
         <v>176</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>177</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>178</v>
-      </c>
-      <c r="D59" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
         <v>180</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>181</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>182</v>
-      </c>
-      <c r="D60" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" t="s">
         <v>184</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>185</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>186</v>
-      </c>
-      <c r="D61" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s">
         <v>189</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>190</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>191</v>
-      </c>
-      <c r="D63" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>192</v>
+      </c>
+      <c r="B64" t="s">
         <v>193</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>194</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>195</v>
-      </c>
-      <c r="D64" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>196</v>
+      </c>
+      <c r="B65" t="s">
         <v>197</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>198</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>199</v>
-      </c>
-      <c r="D65" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" t="s">
         <v>201</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>202</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>203</v>
-      </c>
-      <c r="D66" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" t="s">
         <v>205</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>206</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>207</v>
-      </c>
-      <c r="D67" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>208</v>
+      </c>
+      <c r="B68" t="s">
         <v>209</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>210</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>211</v>
-      </c>
-      <c r="D68" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>212</v>
+      </c>
+      <c r="B69" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" t="s">
         <v>213</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>214</v>
-      </c>
-      <c r="C69" t="s">
-        <v>215</v>
-      </c>
-      <c r="D69" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" t="s">
         <v>218</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>219</v>
-      </c>
-      <c r="C71" t="s">
-        <v>220</v>
-      </c>
-      <c r="D71" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" t="s">
         <v>222</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72" t="s">
         <v>223</v>
-      </c>
-      <c r="C72" t="s">
-        <v>224</v>
-      </c>
-      <c r="D72" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>224</v>
+      </c>
+      <c r="B73" t="s">
+        <v>225</v>
+      </c>
+      <c r="C73" t="s">
         <v>226</v>
       </c>
-      <c r="B73" t="s">
+      <c r="D73" t="s">
         <v>227</v>
-      </c>
-      <c r="C73" t="s">
-        <v>228</v>
-      </c>
-      <c r="D73" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" t="s">
+        <v>229</v>
+      </c>
+      <c r="D74" t="s">
         <v>230</v>
-      </c>
-      <c r="B74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C74" t="s">
-        <v>232</v>
-      </c>
-      <c r="D74" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>232</v>
+      </c>
+      <c r="B76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" t="s">
+        <v>234</v>
+      </c>
+      <c r="D76" t="s">
         <v>235</v>
-      </c>
-      <c r="B76" t="s">
-        <v>236</v>
-      </c>
-      <c r="C76" t="s">
-        <v>237</v>
-      </c>
-      <c r="D76" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>236</v>
+      </c>
+      <c r="B77" t="s">
+        <v>237</v>
+      </c>
+      <c r="C77" t="s">
+        <v>238</v>
+      </c>
+      <c r="D77" t="s">
         <v>239</v>
-      </c>
-      <c r="B77" t="s">
-        <v>240</v>
-      </c>
-      <c r="C77" t="s">
-        <v>241</v>
-      </c>
-      <c r="D77" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>241</v>
+      </c>
+      <c r="B79" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" t="s">
         <v>244</v>
-      </c>
-      <c r="B79" t="s">
-        <v>245</v>
-      </c>
-      <c r="C79" t="s">
-        <v>246</v>
-      </c>
-      <c r="D79" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>245</v>
+      </c>
+      <c r="B80" t="s">
+        <v>246</v>
+      </c>
+      <c r="C80" t="s">
+        <v>247</v>
+      </c>
+      <c r="D80" t="s">
         <v>248</v>
-      </c>
-      <c r="B80" t="s">
-        <v>249</v>
-      </c>
-      <c r="C80" t="s">
-        <v>250</v>
-      </c>
-      <c r="D80" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>249</v>
+      </c>
+      <c r="B81" t="s">
+        <v>250</v>
+      </c>
+      <c r="C81" t="s">
+        <v>251</v>
+      </c>
+      <c r="D81" t="s">
         <v>252</v>
-      </c>
-      <c r="B81" t="s">
-        <v>253</v>
-      </c>
-      <c r="C81" t="s">
-        <v>254</v>
-      </c>
-      <c r="D81" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>253</v>
+      </c>
+      <c r="B82" t="s">
+        <v>254</v>
+      </c>
+      <c r="C82" t="s">
+        <v>255</v>
+      </c>
+      <c r="D82" t="s">
         <v>256</v>
-      </c>
-      <c r="B82" t="s">
-        <v>257</v>
-      </c>
-      <c r="C82" t="s">
-        <v>258</v>
-      </c>
-      <c r="D82" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
